--- a/medical_application_forms/044_medical_office_assistant_application_form--medical_application_forms.xlsx
+++ b/medical_application_forms/044_medical_office_assistant_application_form--medical_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'bachelors',_'label':_'bachelors'}</t>
+          <t>bachelors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'bachelors', 'label': 'Bachelors'}</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'masters',_'label':_'masters'}</t>
+          <t>masters</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'masters', 'label': 'Masters'}</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'doctoral',_'label':_'doctoral'}</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'doctoral', 'label': 'Doctoral'}</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'not_active',_'label':_'not_active'}</t>
+          <t>not_active</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'not_active', 'label': 'Not Active'}</t>
+          <t>Not Active</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
